--- a/08 - Atrib Rest 2025 Gov R1 Papis como peritos.xlsx
+++ b/08 - Atrib Rest 2025 Gov R1 Papis como peritos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maiap\OneDrive\Desktop\Desenvolvimento\Estudo_Atribuicoes_PCSP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2363BB71-45D4-4E6B-AB77-A5DF074C00C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F1215D-8CF8-4A93-BA0B-3B80FC16D4CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9E2F6A9B-94A3-41DD-92E9-2C4405031CDE}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{9E2F6A9B-94A3-41DD-92E9-2C4405031CDE}"/>
   </bookViews>
   <sheets>
     <sheet name="Carreiras e Atribuicoes com cor" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t>mediar conflitos</t>
   </si>
@@ -191,36 +191,6 @@
   </si>
   <si>
     <t>Delegado de Polícia</t>
-  </si>
-  <si>
-    <t>portar arma, distintivo e algemas</t>
-  </si>
-  <si>
-    <t>atender sempre, com urbanidade e eficiência, o público em geral, pessoalmente ou por telefone</t>
-  </si>
-  <si>
-    <t>elaborar, sob orientação da Autoridade Policial, registro de ocorrência</t>
-  </si>
-  <si>
-    <t>conduzir viatura policial</t>
-  </si>
-  <si>
-    <t>cumprir diligência e/ou requisição determinada pela Autoridade Policial, elaborando relatório respectivo</t>
-  </si>
-  <si>
-    <t>proceder à abordagem de pessoas suspeitas da prática de ilícitos, realizando busca pessoal quando necessário</t>
-  </si>
-  <si>
-    <t>identificar pessoas, inclusive por meio digital, nas hipóteses em que tal providência se faça necessária</t>
-  </si>
-  <si>
-    <t>conduzir e apresentar pessoas legalmente presas à Autoridade Policial competente ou onde for por ela determinado</t>
-  </si>
-  <si>
-    <t>auxiliar a Autoridade Policial na formalização de atos de polícia judiciária</t>
-  </si>
-  <si>
-    <t>operar os sistemas de comunicação e de dados da Polícia Civil</t>
   </si>
   <si>
     <t>gestão de polícia judiciária</t>
@@ -1171,62 +1141,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61E66DEB-712A-465C-882E-F5424BC162B6}">
-  <dimension ref="A1:BU10"/>
+  <dimension ref="A1:BK10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="55" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="31.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.44140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="43" max="46" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="55" max="56" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="8" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="69" max="71" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="36" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="45" max="46" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="8" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="59" max="61" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:73" s="1" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:63" s="1" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>57</v>
@@ -1238,214 +1198,184 @@
         <v>59</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="N1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T1" s="3" t="s">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="AD1" s="3" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="AL1" s="3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="AT1" s="3" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="AW1" s="3" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="AX1" s="3" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="AY1" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="AZ1" s="3" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="BA1" s="3" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="BB1" s="3" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="BC1" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="BD1" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="BE1" s="3" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="BF1" s="3" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BG1" s="3" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="BH1" s="3" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="BI1" s="3" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="BJ1" s="3" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="BK1" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="BL1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="BM1" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="BN1" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="BO1" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="BP1" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="BQ1" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="BR1" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="BS1" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="BT1" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="BU1" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>56</v>
       </c>
@@ -1462,34 +1392,34 @@
         <v>1</v>
       </c>
       <c r="F2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" s="5">
         <v>0</v>
@@ -1600,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="AZ2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA2" s="5">
         <v>0</v>
@@ -1630,57 +1560,27 @@
         <v>0</v>
       </c>
       <c r="BJ2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK2" s="5">
         <v>0</v>
       </c>
-      <c r="BL2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU2" s="5">
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="5">
         <v>1</v>
@@ -1695,10 +1595,10 @@
         <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>0</v>
@@ -1713,16 +1613,16 @@
         <v>0</v>
       </c>
       <c r="P3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" s="5">
         <v>0</v>
@@ -1821,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="AZ3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA3" s="5">
         <v>0</v>
@@ -1851,66 +1751,36 @@
         <v>0</v>
       </c>
       <c r="BJ3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK3" s="5">
         <v>0</v>
       </c>
-      <c r="BL3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU3" s="5">
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
         <v>1</v>
@@ -1922,19 +1792,19 @@
         <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="5">
         <v>0</v>
@@ -1943,28 +1813,28 @@
         <v>0</v>
       </c>
       <c r="S4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="5">
         <v>0</v>
@@ -2042,7 +1912,7 @@
         <v>0</v>
       </c>
       <c r="AZ4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA4" s="5">
         <v>0</v>
@@ -2072,75 +1942,45 @@
         <v>0</v>
       </c>
       <c r="BJ4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK4" s="5">
         <v>0</v>
       </c>
-      <c r="BL4" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM4" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN4" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO4" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP4" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ4" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR4" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS4" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT4" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU4" s="5">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
         <v>0</v>
@@ -2158,34 +1998,34 @@
         <v>0</v>
       </c>
       <c r="Q5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA5" s="5">
         <v>1</v>
@@ -2203,34 +2043,34 @@
         <v>1</v>
       </c>
       <c r="AF5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="5">
         <v>1</v>
       </c>
       <c r="AJ5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP5" s="5">
         <v>0</v>
@@ -2242,31 +2082,31 @@
         <v>0</v>
       </c>
       <c r="AS5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT5" s="5">
         <v>0</v>
       </c>
       <c r="AU5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV5" s="5">
         <v>0</v>
       </c>
       <c r="AW5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB5" s="5">
         <v>0</v>
@@ -2278,90 +2118,60 @@
         <v>0</v>
       </c>
       <c r="BE5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF5" s="5">
         <v>0</v>
       </c>
       <c r="BG5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK5" s="5">
-        <v>1</v>
-      </c>
-      <c r="BL5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU5" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="5">
         <v>0</v>
@@ -2388,16 +2198,16 @@
         <v>0</v>
       </c>
       <c r="T6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" s="5">
         <v>0</v>
@@ -2412,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="AB6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC6" s="5">
         <v>0</v>
@@ -2421,7 +2231,7 @@
         <v>1</v>
       </c>
       <c r="AE6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF6" s="5">
         <v>1</v>
@@ -2430,10 +2240,10 @@
         <v>1</v>
       </c>
       <c r="AH6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ6" s="5">
         <v>0</v>
@@ -2442,28 +2252,28 @@
         <v>0</v>
       </c>
       <c r="AL6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM6" s="5">
         <v>0</v>
       </c>
       <c r="AN6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO6" s="5">
         <v>0</v>
       </c>
       <c r="AP6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT6" s="5">
         <v>0</v>
@@ -2481,28 +2291,28 @@
         <v>0</v>
       </c>
       <c r="AY6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA6" s="5">
         <v>0</v>
       </c>
       <c r="BB6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG6" s="5">
         <v>0</v>
@@ -2517,72 +2327,42 @@
         <v>1</v>
       </c>
       <c r="BK6" s="5">
-        <v>0</v>
-      </c>
-      <c r="BL6" s="5">
-        <v>1</v>
-      </c>
-      <c r="BM6" s="5">
-        <v>1</v>
-      </c>
-      <c r="BN6" s="5">
-        <v>1</v>
-      </c>
-      <c r="BO6" s="5">
-        <v>1</v>
-      </c>
-      <c r="BP6" s="5">
-        <v>1</v>
-      </c>
-      <c r="BQ6" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR6" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS6" s="5">
-        <v>1</v>
-      </c>
-      <c r="BT6" s="5">
-        <v>1</v>
-      </c>
-      <c r="BU6" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="5">
         <v>0</v>
@@ -2603,22 +2383,22 @@
         <v>0</v>
       </c>
       <c r="R7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" s="5">
         <v>0</v>
@@ -2633,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="AB7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="5">
         <v>1</v>
@@ -2642,28 +2422,28 @@
         <v>1</v>
       </c>
       <c r="AE7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" s="5">
         <v>0</v>
       </c>
       <c r="AI7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM7" s="5">
         <v>1</v>
@@ -2672,16 +2452,16 @@
         <v>1</v>
       </c>
       <c r="AO7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS7" s="5">
         <v>1</v>
@@ -2690,16 +2470,16 @@
         <v>1</v>
       </c>
       <c r="AU7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY7" s="5">
         <v>1</v>
@@ -2708,16 +2488,16 @@
         <v>1</v>
       </c>
       <c r="BA7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB7" s="5">
         <v>1</v>
       </c>
       <c r="BC7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE7" s="5">
         <v>0</v>
@@ -2732,78 +2512,48 @@
         <v>0</v>
       </c>
       <c r="BI7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK7" s="5">
         <v>0</v>
       </c>
-      <c r="BL7" s="5">
-        <v>1</v>
-      </c>
-      <c r="BM7" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN7" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO7" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP7" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ7" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR7" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS7" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT7" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU7" s="5">
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="5">
         <v>0</v>
@@ -2824,22 +2574,22 @@
         <v>0</v>
       </c>
       <c r="R8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" s="5">
         <v>0</v>
       </c>
       <c r="U8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="5">
         <v>0</v>
       </c>
       <c r="W8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" s="5">
         <v>0</v>
@@ -2854,7 +2604,7 @@
         <v>0</v>
       </c>
       <c r="AB8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="5">
         <v>1</v>
@@ -2863,25 +2613,25 @@
         <v>0</v>
       </c>
       <c r="AE8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="5">
         <v>0</v>
       </c>
       <c r="AG8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH8" s="5">
         <v>0</v>
       </c>
       <c r="AI8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" s="5">
         <v>0</v>
       </c>
       <c r="AK8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL8" s="5">
         <v>0</v>
@@ -2896,28 +2646,28 @@
         <v>0</v>
       </c>
       <c r="AP8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ8" s="5">
         <v>0</v>
       </c>
       <c r="AR8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS8" s="5">
         <v>1</v>
       </c>
       <c r="AT8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV8" s="5">
         <v>0</v>
       </c>
       <c r="AW8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX8" s="5">
         <v>0</v>
@@ -2932,13 +2682,13 @@
         <v>0</v>
       </c>
       <c r="BB8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE8" s="5">
         <v>0</v>
@@ -2956,81 +2706,51 @@
         <v>0</v>
       </c>
       <c r="BJ8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK8" s="5">
         <v>0</v>
       </c>
-      <c r="BL8" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM8" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN8" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO8" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP8" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ8" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR8" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS8" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT8" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU8" s="5">
-        <v>0</v>
-      </c>
     </row>
-    <row r="9" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="5">
         <v>0</v>
       </c>
       <c r="M9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="5">
         <v>0</v>
@@ -3078,7 +2798,7 @@
         <v>0</v>
       </c>
       <c r="AC9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD9" s="5">
         <v>0</v>
@@ -3090,13 +2810,13 @@
         <v>0</v>
       </c>
       <c r="AG9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH9" s="5">
         <v>0</v>
       </c>
       <c r="AI9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" s="5">
         <v>0</v>
@@ -3108,10 +2828,10 @@
         <v>0</v>
       </c>
       <c r="AM9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO9" s="5">
         <v>0</v>
@@ -3120,25 +2840,25 @@
         <v>0</v>
       </c>
       <c r="AQ9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR9" s="5">
         <v>0</v>
       </c>
       <c r="AS9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT9" s="5">
         <v>0</v>
       </c>
       <c r="AU9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX9" s="5">
         <v>1</v>
@@ -3147,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="AZ9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA9" s="5">
         <v>1</v>
@@ -3162,90 +2882,60 @@
         <v>0</v>
       </c>
       <c r="BE9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI9" s="5">
         <v>0</v>
       </c>
       <c r="BJ9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK9" s="5">
-        <v>1</v>
-      </c>
-      <c r="BL9" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM9" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN9" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO9" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP9" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ9" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR9" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS9" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT9" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU9" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="5">
         <v>0</v>
@@ -3281,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="W10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" s="5">
         <v>0</v>
@@ -3296,7 +2986,7 @@
         <v>0</v>
       </c>
       <c r="AB10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC10" s="5">
         <v>0</v>
@@ -3311,13 +3001,13 @@
         <v>0</v>
       </c>
       <c r="AG10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH10" s="5">
         <v>0</v>
       </c>
       <c r="AI10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ10" s="5">
         <v>0</v>
@@ -3326,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="AL10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM10" s="5">
         <v>0</v>
@@ -3347,7 +3037,7 @@
         <v>0</v>
       </c>
       <c r="AS10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT10" s="5">
         <v>0</v>
@@ -3368,74 +3058,44 @@
         <v>0</v>
       </c>
       <c r="AZ10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA10" s="5">
         <v>0</v>
       </c>
       <c r="BB10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BI10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ10" s="5">
         <v>1</v>
       </c>
       <c r="BK10" s="5">
-        <v>0</v>
-      </c>
-      <c r="BL10" s="5">
-        <v>1</v>
-      </c>
-      <c r="BM10" s="5">
-        <v>1</v>
-      </c>
-      <c r="BN10" s="5">
-        <v>1</v>
-      </c>
-      <c r="BO10" s="5">
-        <v>1</v>
-      </c>
-      <c r="BP10" s="5">
-        <v>1</v>
-      </c>
-      <c r="BQ10" s="5">
-        <v>1</v>
-      </c>
-      <c r="BR10" s="5">
-        <v>1</v>
-      </c>
-      <c r="BS10" s="5">
-        <v>1</v>
-      </c>
-      <c r="BT10" s="5">
-        <v>1</v>
-      </c>
-      <c r="BU10" s="5">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:BU10">
+  <conditionalFormatting sqref="B2:BK10">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
